--- a/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица КИ.xlsx
@@ -8,19 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\матрицы ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31DBF47-B087-47F1-835B-4DA29B8721A7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378ED350-1F2A-4354-A74C-AA9107F38869}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -568,12 +576,6 @@
     <t>SU004016</t>
   </si>
   <si>
-    <t xml:space="preserve"> 547  Колбаса Мясная Классическая ТМ Вязанка в оболочке полиамид. ВЕС  ПОКОМ</t>
-  </si>
-  <si>
-    <t>SU004157</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 551  Колбаса Сливушка ТМ Вязанка в модифицированной газовой среде 0,11 кг нарезка  ПОКОМ</t>
   </si>
   <si>
@@ -761,9 +763,6 @@
   </si>
   <si>
     <t>SU</t>
-  </si>
-  <si>
-    <t>вывод</t>
   </si>
 </sst>
 </file>
@@ -779,7 +778,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -789,12 +788,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -826,20 +819,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1120,7 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
@@ -1133,13 +1121,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2223,44 +2211,40 @@
       <c r="D91" s="1"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="5">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D92" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D92" s="1"/>
+    </row>
+    <row r="93" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D93" s="1"/>
+      <c r="D93" s="4"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="3">
+      <c r="A94" s="2">
         <v>93</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D94" s="4" t="s">
-        <v>244</v>
-      </c>
+      <c r="D94" s="1"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
@@ -2326,13 +2310,15 @@
       <c r="A100" s="2">
         <v>99</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D100" s="1"/>
+      <c r="D100" s="3" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
@@ -2585,18 +2571,6 @@
         <v>240</v>
       </c>
       <c r="D121" s="1"/>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="2">
-        <v>121</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D122" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица КИ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\матрицы ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378ED350-1F2A-4354-A74C-AA9107F38869}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4B43A5-79A6-4E11-B82D-EA65E6889AA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="246">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -763,6 +763,9 @@
   </si>
   <si>
     <t>SU</t>
+  </si>
+  <si>
+    <t>ВЫВОД</t>
   </si>
 </sst>
 </file>
@@ -778,7 +781,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -788,6 +791,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -819,7 +828,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -828,6 +837,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1875,16 +1888,18 @@
       <c r="D63" s="1"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+      <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="D64" s="1"/>
+      <c r="D64" s="7" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
@@ -2321,16 +2336,18 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="2">
+      <c r="A101" s="6">
         <v>100</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="D101" s="1"/>
+      <c r="D101" s="7" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2">

--- a/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/матрицы ПОКОМ/матрица КИ.xlsx
@@ -8,13 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\матрицы ПОКОМ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4B43A5-79A6-4E11-B82D-EA65E6889AA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8869CC45-DAEE-4313-810F-B8B87231E069}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$D$124</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -28,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="258">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -766,6 +772,42 @@
   </si>
   <si>
     <t>ВЫВОД</t>
+  </si>
+  <si>
+    <t>SU004314</t>
+  </si>
+  <si>
+    <t>Колбаса варено-копченая Сервелат Европейский ТМ Вязанка вес</t>
+  </si>
+  <si>
+    <t>ВВОД</t>
+  </si>
+  <si>
+    <t>SU002971</t>
+  </si>
+  <si>
+    <t>Сардельки «Шпикачки Зареченские» Весовой полиамид ТМ «Зареченские продукты»</t>
+  </si>
+  <si>
+    <t>SU001340</t>
+  </si>
+  <si>
+    <t>Сосиски Ганноверские Бордо Весовые П/а мгс Баварушка</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мариуполь</t>
+  </si>
+  <si>
+    <t>ДНР</t>
+  </si>
+  <si>
+    <t>ЛНР</t>
   </si>
 </sst>
 </file>
@@ -781,7 +823,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -797,6 +839,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -828,7 +882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -841,6 +895,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -856,6 +915,117 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="КИ"/>
+      <sheetName val="ЗПФ"/>
+      <sheetName val="Вывод КИ"/>
+      <sheetName val="Вывод ЗПФ"/>
+      <sheetName val="Лист2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2">
+        <row r="4">
+          <cell r="E4" t="str">
+            <v xml:space="preserve">Ввод </v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>Мелитополь</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>Бердянск</v>
+          </cell>
+          <cell r="I4" t="str">
+            <v>Мариуполь</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>ДНР</v>
+          </cell>
+          <cell r="K4" t="str">
+            <v>ЛНР</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5" t="str">
+            <v>SU004314</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>Колбаса варено-копченая Сервелат Европейский ТМ Вязанка вес</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>100кг</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>100кг</v>
+          </cell>
+          <cell r="I5" t="str">
+            <v>100кг</v>
+          </cell>
+          <cell r="J5" t="str">
+            <v>150кг</v>
+          </cell>
+          <cell r="K5" t="str">
+            <v>200кг</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6" t="str">
+            <v>SU002971</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>Сардельки «Шпикачки Зареченские» Весовой полиамид ТМ «Зареченские продукты»</v>
+          </cell>
+          <cell r="G6">
+            <v>0</v>
+          </cell>
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+          <cell r="K6" t="str">
+            <v>100кг</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="E7" t="str">
+            <v>SU001340</v>
+          </cell>
+          <cell r="F7" t="str">
+            <v>Сосиски Ганноверские Бордо Весовые П/а мгс Баварушка</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+          <cell r="I7">
+            <v>0</v>
+          </cell>
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+          <cell r="K7" t="str">
+            <v>100кг</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1121,15 +1291,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D121"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="3" max="3" width="101" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1142,8 +1314,23 @@
       <c r="D1" s="1" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1155,7 +1342,7 @@
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1167,7 +1354,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1179,7 +1366,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1191,7 +1378,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1203,7 +1390,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1215,7 +1402,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1227,7 +1414,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1239,7 +1426,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1251,7 +1438,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1263,7 +1450,7 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1275,7 +1462,7 @@
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1287,7 +1474,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1299,7 +1486,7 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1311,7 +1498,7 @@
       </c>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1323,7 +1510,7 @@
       </c>
       <c r="D16" s="1"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1335,7 +1522,7 @@
       </c>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1347,7 +1534,7 @@
       </c>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1359,7 +1546,7 @@
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1371,7 +1558,7 @@
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1383,7 +1570,7 @@
       </c>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1395,7 +1582,7 @@
       </c>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1407,7 +1594,7 @@
       </c>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1419,7 +1606,7 @@
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1431,7 +1618,7 @@
       </c>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1443,7 +1630,7 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1455,7 +1642,7 @@
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1467,7 +1654,7 @@
       </c>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1479,7 +1666,7 @@
       </c>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1491,7 +1678,7 @@
       </c>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1503,7 +1690,7 @@
       </c>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1515,7 +1702,7 @@
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1527,7 +1714,7 @@
       </c>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1539,7 +1726,7 @@
       </c>
       <c r="D34" s="1"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1551,7 +1738,7 @@
       </c>
       <c r="D35" s="1"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1563,7 +1750,7 @@
       </c>
       <c r="D36" s="1"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1575,7 +1762,7 @@
       </c>
       <c r="D37" s="1"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1587,7 +1774,7 @@
       </c>
       <c r="D38" s="1"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1599,7 +1786,7 @@
       </c>
       <c r="D39" s="1"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1611,7 +1798,7 @@
       </c>
       <c r="D40" s="1"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1623,7 +1810,7 @@
       </c>
       <c r="D41" s="1"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1635,7 +1822,7 @@
       </c>
       <c r="D42" s="1"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1647,7 +1834,7 @@
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1659,7 +1846,7 @@
       </c>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1671,7 +1858,7 @@
       </c>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -1683,7 +1870,7 @@
       </c>
       <c r="D46" s="1"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -1695,7 +1882,7 @@
       </c>
       <c r="D47" s="1"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -1707,7 +1894,7 @@
       </c>
       <c r="D48" s="1"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -1719,7 +1906,7 @@
       </c>
       <c r="D49" s="1"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -1731,7 +1918,7 @@
       </c>
       <c r="D50" s="1"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -1743,7 +1930,7 @@
       </c>
       <c r="D51" s="1"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -1755,7 +1942,7 @@
       </c>
       <c r="D52" s="1"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -1767,7 +1954,7 @@
       </c>
       <c r="D53" s="1"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -1779,7 +1966,7 @@
       </c>
       <c r="D54" s="1"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -1791,7 +1978,7 @@
       </c>
       <c r="D55" s="1"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -1803,7 +1990,7 @@
       </c>
       <c r="D56" s="1"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -1815,7 +2002,7 @@
       </c>
       <c r="D57" s="1"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -1827,7 +2014,7 @@
       </c>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -1839,7 +2026,7 @@
       </c>
       <c r="D59" s="1"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -1851,7 +2038,7 @@
       </c>
       <c r="D60" s="1"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -1863,7 +2050,7 @@
       </c>
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -1875,7 +2062,7 @@
       </c>
       <c r="D62" s="1"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -1901,7 +2088,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -1913,7 +2100,7 @@
       </c>
       <c r="D65" s="1"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -1925,7 +2112,7 @@
       </c>
       <c r="D66" s="1"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -1937,7 +2124,7 @@
       </c>
       <c r="D67" s="1"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -1949,7 +2136,7 @@
       </c>
       <c r="D68" s="1"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -1961,7 +2148,7 @@
       </c>
       <c r="D69" s="1"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -1973,7 +2160,7 @@
       </c>
       <c r="D70" s="1"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -1985,7 +2172,7 @@
       </c>
       <c r="D71" s="1"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -1997,7 +2184,7 @@
       </c>
       <c r="D72" s="1"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2009,7 +2196,7 @@
       </c>
       <c r="D73" s="1"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2021,7 +2208,7 @@
       </c>
       <c r="D74" s="1"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2033,7 +2220,7 @@
       </c>
       <c r="D75" s="1"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2045,7 +2232,7 @@
       </c>
       <c r="D76" s="1"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2057,7 +2244,7 @@
       </c>
       <c r="D77" s="1"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -2069,7 +2256,7 @@
       </c>
       <c r="D78" s="1"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -2081,7 +2268,7 @@
       </c>
       <c r="D79" s="1"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -2093,7 +2280,7 @@
       </c>
       <c r="D80" s="1"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -2105,7 +2292,7 @@
       </c>
       <c r="D81" s="1"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -2117,7 +2304,7 @@
       </c>
       <c r="D82" s="1"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -2129,7 +2316,7 @@
       </c>
       <c r="D83" s="1"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -2141,7 +2328,7 @@
       </c>
       <c r="D84" s="1"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -2153,7 +2340,7 @@
       </c>
       <c r="D85" s="1"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -2165,7 +2352,7 @@
       </c>
       <c r="D86" s="1"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -2177,7 +2364,7 @@
       </c>
       <c r="D87" s="1"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -2189,7 +2376,7 @@
       </c>
       <c r="D88" s="1"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -2201,7 +2388,7 @@
       </c>
       <c r="D89" s="1"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -2213,7 +2400,7 @@
       </c>
       <c r="D90" s="1"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -2225,7 +2412,7 @@
       </c>
       <c r="D91" s="1"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -2237,7 +2424,7 @@
       </c>
       <c r="D92" s="1"/>
     </row>
-    <row r="93" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -2249,7 +2436,7 @@
       </c>
       <c r="D93" s="4"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -2261,7 +2448,7 @@
       </c>
       <c r="D94" s="1"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -2273,7 +2460,7 @@
       </c>
       <c r="D95" s="1"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -2285,7 +2472,7 @@
       </c>
       <c r="D96" s="1"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -2297,7 +2484,7 @@
       </c>
       <c r="D97" s="1"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -2309,7 +2496,7 @@
       </c>
       <c r="D98" s="1"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -2321,7 +2508,7 @@
       </c>
       <c r="D99" s="1"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -2349,7 +2536,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -2361,7 +2548,7 @@
       </c>
       <c r="D102" s="1"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -2373,7 +2560,7 @@
       </c>
       <c r="D103" s="1"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -2385,7 +2572,7 @@
       </c>
       <c r="D104" s="1"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -2397,7 +2584,7 @@
       </c>
       <c r="D105" s="1"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -2409,7 +2596,7 @@
       </c>
       <c r="D106" s="1"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -2421,7 +2608,7 @@
       </c>
       <c r="D107" s="1"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -2433,7 +2620,7 @@
       </c>
       <c r="D108" s="1"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -2445,7 +2632,7 @@
       </c>
       <c r="D109" s="1"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -2457,7 +2644,7 @@
       </c>
       <c r="D110" s="1"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -2469,7 +2656,7 @@
       </c>
       <c r="D111" s="1"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -2481,7 +2668,7 @@
       </c>
       <c r="D112" s="1"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -2493,7 +2680,7 @@
       </c>
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -2505,7 +2692,7 @@
       </c>
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -2517,7 +2704,7 @@
       </c>
       <c r="D115" s="1"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -2529,7 +2716,7 @@
       </c>
       <c r="D116" s="1"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -2541,7 +2728,7 @@
       </c>
       <c r="D117" s="1"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -2553,7 +2740,7 @@
       </c>
       <c r="D118" s="1"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -2565,7 +2752,7 @@
       </c>
       <c r="D119" s="1"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -2577,7 +2764,7 @@
       </c>
       <c r="D120" s="1"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -2589,7 +2776,108 @@
       </c>
       <c r="D121" s="1"/>
     </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B122" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E122" s="10" t="str">
+        <f>VLOOKUP(B122,'[1]Вывод КИ'!$E:$K,3,0)</f>
+        <v>100кг</v>
+      </c>
+      <c r="F122" s="10" t="str">
+        <f>VLOOKUP(B122,'[1]Вывод КИ'!$E:$K,4,0)</f>
+        <v>100кг</v>
+      </c>
+      <c r="G122" s="10" t="str">
+        <f>VLOOKUP(B122,'[1]Вывод КИ'!$E:$K,5,0)</f>
+        <v>100кг</v>
+      </c>
+      <c r="H122" s="10" t="str">
+        <f>VLOOKUP(B122,'[1]Вывод КИ'!$E:$K,6,0)</f>
+        <v>150кг</v>
+      </c>
+      <c r="I122" s="10" t="str">
+        <f>VLOOKUP(B122,'[1]Вывод КИ'!$E:$K,7,0)</f>
+        <v>200кг</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B123" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E123">
+        <f>VLOOKUP(B123,'[1]Вывод КИ'!$E:$K,3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <f>VLOOKUP(B123,'[1]Вывод КИ'!$E:$K,4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <f>VLOOKUP(B123,'[1]Вывод КИ'!$E:$K,5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <f>VLOOKUP(B123,'[1]Вывод КИ'!$E:$K,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I123" s="10" t="str">
+        <f>VLOOKUP(B123,'[1]Вывод КИ'!$E:$K,7,0)</f>
+        <v>100кг</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B124" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="E124">
+        <f>VLOOKUP(B124,'[1]Вывод КИ'!$E:$K,3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <f>VLOOKUP(B124,'[1]Вывод КИ'!$E:$K,4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <f>VLOOKUP(B124,'[1]Вывод КИ'!$E:$K,5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <f>VLOOKUP(B124,'[1]Вывод КИ'!$E:$K,6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I124" s="10" t="str">
+        <f>VLOOKUP(B124,'[1]Вывод КИ'!$E:$K,7,0)</f>
+        <v>100кг</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D124" xr:uid="{69EE1CF2-156F-4B58-9E27-B150F9B22FF9}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="ВВОД"/>
+        <filter val="ВЫВОД"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>